--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N143_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N143_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>41.24266836198866</v>
+        <v>6.701933608823158</v>
       </c>
       <c r="D2" t="n">
-        <v>40.99371938951089</v>
+        <v>6.66147940079552</v>
       </c>
       <c r="E2" t="n">
-        <v>8.537579288790369</v>
+        <v>1.387356634428435</v>
       </c>
       <c r="F2" t="n">
-        <v>14.99769797450876</v>
+        <v>2.437125920857673</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>29.58394285459557</v>
+        <v>4.80739071387178</v>
       </c>
       <c r="D3" t="n">
-        <v>29.36429766237275</v>
+        <v>4.771698370135572</v>
       </c>
       <c r="E3" t="n">
-        <v>8.537579288790369</v>
+        <v>1.387356634428435</v>
       </c>
       <c r="F3" t="n">
-        <v>14.99769797450876</v>
+        <v>2.437125920857673</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>55.39999862290956</v>
+        <v>9.002499776222804</v>
       </c>
       <c r="D4" t="n">
-        <v>54.53914235517115</v>
+        <v>8.862610632715313</v>
       </c>
       <c r="E4" t="n">
-        <v>8.537579288790369</v>
+        <v>1.387356634428435</v>
       </c>
       <c r="F4" t="n">
-        <v>14.99769797450876</v>
+        <v>2.437125920857673</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>41.71134388586566</v>
+        <v>6.77809338145317</v>
       </c>
       <c r="D5" t="n">
-        <v>41.5666024747289</v>
+        <v>6.754572902143446</v>
       </c>
       <c r="E5" t="n">
-        <v>8.537579288790369</v>
+        <v>1.387356634428435</v>
       </c>
       <c r="F5" t="n">
-        <v>14.99769797450876</v>
+        <v>2.437125920857673</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>29.35665361097059</v>
+        <v>4.770456211782721</v>
       </c>
       <c r="D6" t="n">
-        <v>29.37651611742879</v>
+        <v>4.773683869082178</v>
       </c>
       <c r="E6" t="n">
-        <v>8.537579288790369</v>
+        <v>1.387356634428435</v>
       </c>
       <c r="F6" t="n">
-        <v>14.99769797450876</v>
+        <v>2.437125920857673</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>29.92879437843728</v>
+        <v>4.863429086496058</v>
       </c>
       <c r="D7" t="n">
-        <v>29.82164616980737</v>
+        <v>4.846017502593697</v>
       </c>
       <c r="E7" t="n">
-        <v>8.537579288790369</v>
+        <v>1.387356634428435</v>
       </c>
       <c r="F7" t="n">
-        <v>14.99769797450876</v>
+        <v>2.437125920857673</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>30.74861466870689</v>
+        <v>4.99664988366487</v>
       </c>
       <c r="D8" t="n">
-        <v>29.69958501634095</v>
+        <v>4.826182565155405</v>
       </c>
       <c r="E8" t="n">
-        <v>8.537579288790369</v>
+        <v>1.387356634428435</v>
       </c>
       <c r="F8" t="n">
-        <v>14.99769797450876</v>
+        <v>2.437125920857673</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>45.60150943159076</v>
+        <v>7.410245282633498</v>
       </c>
       <c r="D9" t="n">
-        <v>43.9480327673604</v>
+        <v>7.141555324696064</v>
       </c>
       <c r="E9" t="n">
-        <v>8.537579288790369</v>
+        <v>1.387356634428435</v>
       </c>
       <c r="F9" t="n">
-        <v>14.99769797450876</v>
+        <v>2.437125920857673</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>34.958187249811</v>
+        <v>5.680705428094288</v>
       </c>
       <c r="D10" t="n">
-        <v>77.26687526304634</v>
+        <v>12.55586723024503</v>
       </c>
       <c r="E10" t="n">
-        <v>8.537579288790369</v>
+        <v>1.387356634428435</v>
       </c>
       <c r="F10" t="n">
-        <v>14.99769797450876</v>
+        <v>2.437125920857673</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
